--- a/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,6 +878,40 @@
         <v>45</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>signal_relay</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>building.signal_relay.name</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>40</v>
+      </c>
+      <c r="J13" t="n">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,6 +912,74 @@
         <v>25</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>power_pole</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>building.power_pole.name</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>power_pole_t2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>building.power_pole_t2.name</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -980,6 +980,244 @@
         <v>10</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>recycler</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>building.recycler.name</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>40</v>
+      </c>
+      <c r="J16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>extraction_drill</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>building.extraction_drill.name</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>30</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>refinery_furnace</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>building.refinery_furnace.name</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>40</v>
+      </c>
+      <c r="J18" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>refinery_tower</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>building.refinery_tower.name</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>80</v>
+      </c>
+      <c r="J19" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>blending_station</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>building.blending_station.name</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>8</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>50</v>
+      </c>
+      <c r="J20" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>waste_pond</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>building.waste_pond.name</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>30</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>fluid_pump</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>building.fluid_pump.name</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>30</v>
+      </c>
+      <c r="J22" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1218,6 +1218,142 @@
         <v>20</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>parts_workshop</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>building.parts_workshop.name</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>50</v>
+      </c>
+      <c r="J23" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>electronics_bench</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>building.electronics_bench.name</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>60</v>
+      </c>
+      <c r="J24" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>component_workshop</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>building.component_workshop.name</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>80</v>
+      </c>
+      <c r="J25" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>firmware_burner</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>building.firmware_burner.name</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>60</v>
+      </c>
+      <c r="J26" t="n">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1354,6 +1354,108 @@
         <v>35</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>fuel_generator</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>building.fuel_generator.name</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>300</v>
+      </c>
+      <c r="G27" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" t="n">
+        <v>20</v>
+      </c>
+      <c r="I27" t="n">
+        <v>70</v>
+      </c>
+      <c r="J27" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>solar_array</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>building.solar_array.name</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>60</v>
+      </c>
+      <c r="G28" t="n">
+        <v>20</v>
+      </c>
+      <c r="H28" t="n">
+        <v>15</v>
+      </c>
+      <c r="I28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J28" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>energy_storage</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>building.energy_storage.name</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>20</v>
+      </c>
+      <c r="H29" t="n">
+        <v>15</v>
+      </c>
+      <c r="I29" t="n">
+        <v>60</v>
+      </c>
+      <c r="J29" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1456,6 +1456,40 @@
         <v>30</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>override_array</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>building.override_array.name</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>80</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>120</v>
+      </c>
+      <c r="J30" t="n">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1490,6 +1490,40 @@
         <v>50</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>sim_lab</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>building.sim_lab.name</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>15</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>60</v>
+      </c>
+      <c r="J31" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1524,6 +1524,40 @@
         <v>30</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>test_range</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>building.test_range.name</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>80</v>
+      </c>
+      <c r="J32" t="n">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1558,6 +1558,40 @@
         <v>40</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>circuit_synth</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>building.circuit_synth.name</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>8</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>60</v>
+      </c>
+      <c r="J33" t="n">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1592,6 +1592,40 @@
         <v>35</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>listening_post</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>building.listening_post.name</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>80</v>
+      </c>
+      <c r="J34" t="n">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1626,6 +1626,40 @@
         <v>40</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>blackbox_gallery</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>building.blackbox_gallery.name</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>60</v>
+      </c>
+      <c r="J35" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1660,6 +1660,74 @@
         <v>30</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>turret_light</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>building.turret_light.name</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>8</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>50</v>
+      </c>
+      <c r="J36" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>turret_heavy</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>building.turret_heavy.name</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>15</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>90</v>
+      </c>
+      <c r="J37" t="n">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1728,6 +1728,210 @@
         <v>40</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>barrier_t1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>building.barrier_t1.name</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>barrier_t2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>building.barrier_t2.name</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>6</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>barrier_t3</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>building.barrier_t3.name</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>10</v>
+      </c>
+      <c r="J40" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>gate</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>building.gate.name</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>12</v>
+      </c>
+      <c r="J41" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>shield_gen</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>building.shield_gen.name</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>60</v>
+      </c>
+      <c r="J42" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trap_emitter</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>building.trap_emitter.name</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J43" t="n">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1932,6 +1932,40 @@
         <v>18</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>repair_drone_station</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>building.repair_drone_station.name</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>12</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>70</v>
+      </c>
+      <c r="J44" t="n">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1966,6 +1966,40 @@
         <v>35</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>building.purifier.name</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>12</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>60</v>
+      </c>
+      <c r="J45" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
+++ b/Configs/GameConfig/Datas/fg/#Building-建筑.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1970,16 +1970,16 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>purifier</t>
+          <t>drop_station</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>building.purifier.name</t>
+          <t>building.drop_station.name</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E45" t="n">
         <v>3</v>
@@ -1994,9 +1994,43 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
+        <v>160</v>
+      </c>
+      <c r="J45" t="n">
         <v>60</v>
       </c>
-      <c r="J45" t="n">
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>purifier</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>building.purifier.name</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>12</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>60</v>
+      </c>
+      <c r="J46" t="n">
         <v>30</v>
       </c>
     </row>
